--- a/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9726_liceo-teniente-francisco-mery-aguirre_nt2_rubricas.xlsx
@@ -1956,13 +1956,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2D0052F-52BB-4610-9729-B7786DF18080}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{379AABAA-7DE4-4DF0-B8CC-E7C498F2D6AB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{54D14D39-8F92-452C-BE77-233976EE1943}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D3E67932-FB3A-4407-9EE2-2C8F8E1FEAA7}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DB79915-0F6C-4F6B-8BDE-E948EAD2011E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96C52A59-985D-4752-8638-940D9EC11111}"/>
 </file>